--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.4.4_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.4.4_RTO_Pretty.xlsx
@@ -819,7 +819,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Engine v3.4.3  ·  Generated 25 Jun 2026  ·  Phase-1 Conservative plan  ·  35-min headway ceiling</t>
+          <t>Engine v3.4.3  ·  Generated 26 Jun 2026  ·  Phase-1 Conservative plan  ·  35-min headway ceiling</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="D52" s="38" t="n">
-        <v>6.5</v>
+        <v>6.356</v>
       </c>
       <c r="E52" s="39" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>35</v>
       </c>
       <c r="H52" s="38" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
       <c r="I52" s="41" t="n">
         <v>3</v>
@@ -10501,7 +10501,7 @@
         </is>
       </c>
       <c r="D184" s="50" t="n">
-        <v>54.466</v>
+        <v>37.093</v>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>15</v>
       </c>
       <c r="H184" s="38" t="n">
-        <v>163.4</v>
+        <v>111.3</v>
       </c>
       <c r="I184" s="41" t="n">
         <v>13</v>
